--- a/03_Private_Equity/_template_LBO.xlsx
+++ b/03_Private_Equity/_template_LBO.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="78">
   <si>
     <t xml:space="preserve">[TARGET] — LBO Model</t>
   </si>
@@ -39,13 +39,16 @@
     <t xml:space="preserve">LBO / take-private / add-on</t>
   </si>
   <si>
+    <t xml:space="preserve">Last refreshed:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[date]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Next covenant/refinancing date:</t>
+  </si>
+  <si>
     <t xml:space="preserve">Entry date:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[date]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Last refreshed:</t>
   </si>
   <si>
     <t xml:space="preserve">Hold period (yrs):</t>
@@ -419,112 +422,108 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -780,64 +779,72 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:C9"/>
+  <dimension ref="B2:C10"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="4"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="4"/>
+      <c r="C4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="2" t="s">
         <v>9</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -859,126 +866,126 @@
   <dimension ref="B2:F13"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>10</v>
+      <c r="B2" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="E4" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="7" t="n">
+      <c r="C5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="C6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="7" t="n">
+      <c r="C7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="C8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="C9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="8" t="n">
+      <c r="C10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="7" t="n">
         <f aca="false">SUM(F5:F9)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="8" t="n">
+      <c r="B11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="7" t="n">
         <f aca="false">SUM(C5:C10)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="9" t="n">
+      <c r="B13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="8" t="n">
         <f aca="false">C11-F10</f>
         <v>0</v>
       </c>
@@ -1002,350 +1009,350 @@
   <dimension ref="B2:K16"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>27</v>
+      <c r="B2" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="E4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="F4" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="G4" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="H4" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="K4" s="11"/>
+      <c r="J4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" s="10"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="13" t="n">
+      <c r="B5" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="12" t="n">
         <f aca="false">Returns!C5</f>
         <v>0</v>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="13" t="n">
         <f aca="false">C5*(1+$K$5)</f>
         <v>0</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="13" t="n">
         <f aca="false">D5*(1+$K$5)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="14" t="n">
+      <c r="F5" s="13" t="n">
         <f aca="false">E5*(1+$K$5)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="14" t="n">
+      <c r="G5" s="13" t="n">
         <f aca="false">F5*(1+$K$5)</f>
         <v>0</v>
       </c>
-      <c r="H5" s="14" t="n">
+      <c r="H5" s="13" t="n">
         <f aca="false">G5*(1+$K$5)</f>
         <v>0</v>
       </c>
-      <c r="J5" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="K5" s="15" t="n">
+      <c r="J5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="K5" s="14" t="n">
         <v>0.05</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="14" t="n">
+      <c r="B6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="13" t="n">
         <f aca="false">C5*$K$6</f>
         <v>0</v>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="13" t="n">
         <f aca="false">D5*$K$6</f>
         <v>0</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="13" t="n">
         <f aca="false">E5*$K$6</f>
         <v>0</v>
       </c>
-      <c r="F6" s="14" t="n">
+      <c r="F6" s="13" t="n">
         <f aca="false">F5*$K$6</f>
         <v>0</v>
       </c>
-      <c r="G6" s="14" t="n">
+      <c r="G6" s="13" t="n">
         <f aca="false">G5*$K$6</f>
         <v>0</v>
       </c>
-      <c r="H6" s="14" t="n">
+      <c r="H6" s="13" t="n">
         <f aca="false">H5*$K$6</f>
         <v>0</v>
       </c>
-      <c r="J6" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="K6" s="15" t="n">
+      <c r="J6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="K6" s="14" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J7" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="K7" s="15" t="n">
+      <c r="J7" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K7" s="14" t="n">
         <v>0.01</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="K8" s="15" t="n">
+      <c r="B8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="K8" s="14" t="n">
         <v>0.75</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="16" t="n">
+      <c r="B9" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="15" t="n">
         <f aca="false">$K$10</f>
         <v>0</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="15" t="n">
         <f aca="false">C12</f>
         <v>0</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="15" t="n">
         <f aca="false">D12</f>
         <v>0</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="15" t="n">
         <f aca="false">E12</f>
         <v>0</v>
       </c>
-      <c r="G9" s="16" t="n">
+      <c r="G9" s="15" t="n">
         <f aca="false">F12</f>
         <v>0</v>
       </c>
-      <c r="H9" s="16" t="n">
+      <c r="H9" s="15" t="n">
         <f aca="false">G12</f>
         <v>0</v>
       </c>
-      <c r="J9" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="K9" s="17" t="n">
+      <c r="J9" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="K9" s="16" t="n">
         <v>0.09</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="16" t="n">
+      <c r="B10" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="15" t="n">
         <f aca="false">MIN($K$10*$K$7,C9)</f>
         <v>0</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="15" t="n">
         <f aca="false">MIN($K$10*$K$7,D9)</f>
         <v>0</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="15" t="n">
         <f aca="false">MIN($K$10*$K$7,E9)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="15" t="n">
         <f aca="false">MIN($K$10*$K$7,F9)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="16" t="n">
+      <c r="G10" s="15" t="n">
         <f aca="false">MIN($K$10*$K$7,G9)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="16" t="n">
+      <c r="H10" s="15" t="n">
         <f aca="false">MIN($K$10*$K$7,H9)</f>
         <v>0</v>
       </c>
-      <c r="J10" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="K10" s="13" t="n">
+      <c r="J10" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="K10" s="12" t="n">
         <f aca="false">'Sources &amp; Uses'!C7</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="16" t="n">
+      <c r="B11" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="15" t="n">
         <f aca="false">MIN(MAX(0,$K$8*(C6-C10-C13)),C9-C10)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="15" t="n">
         <f aca="false">MIN(MAX(0,$K$8*(D6-D10-D13)),D9-D10)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="15" t="n">
         <f aca="false">MIN(MAX(0,$K$8*(E6-E10-E13)),E9-E10)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="15" t="n">
         <f aca="false">MIN(MAX(0,$K$8*(F6-F10-F13)),F9-F10)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="16" t="n">
+      <c r="G11" s="15" t="n">
         <f aca="false">MIN(MAX(0,$K$8*(G6-G10-G13)),G9-G10)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="16" t="n">
+      <c r="H11" s="15" t="n">
         <f aca="false">MIN(MAX(0,$K$8*(H6-H10-H13)),H9-H10)</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="16" t="n">
+      <c r="B12" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="15" t="n">
         <f aca="false">C9-C10-C11</f>
         <v>0</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="15" t="n">
         <f aca="false">D9-D10-D11</f>
         <v>0</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="15" t="n">
         <f aca="false">E9-E10-E11</f>
         <v>0</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="15" t="n">
         <f aca="false">F9-F10-F11</f>
         <v>0</v>
       </c>
-      <c r="G12" s="16" t="n">
+      <c r="G12" s="15" t="n">
         <f aca="false">G9-G10-G11</f>
         <v>0</v>
       </c>
-      <c r="H12" s="16" t="n">
+      <c r="H12" s="15" t="n">
         <f aca="false">H9-H10-H11</f>
         <v>0</v>
       </c>
-      <c r="J12" s="19" t="s">
-        <v>47</v>
+      <c r="J12" s="18" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="16" t="n">
+      <c r="B13" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="15" t="n">
         <f aca="false">C9*$K$9</f>
         <v>0</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="15" t="n">
         <f aca="false">D9*$K$9</f>
         <v>0</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="15" t="n">
         <f aca="false">E9*$K$9</f>
         <v>0</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="15" t="n">
         <f aca="false">F9*$K$9</f>
         <v>0</v>
       </c>
-      <c r="G13" s="16" t="n">
+      <c r="G13" s="15" t="n">
         <f aca="false">G9*$K$9</f>
         <v>0</v>
       </c>
-      <c r="H13" s="16" t="n">
+      <c r="H13" s="15" t="n">
         <f aca="false">H9*$K$9</f>
         <v>0</v>
       </c>
-      <c r="J13" s="19" t="s">
-        <v>49</v>
+      <c r="J13" s="18" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" s="9" t="n">
+      <c r="B15" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="8" t="n">
         <f aca="false">C12</f>
         <v>0</v>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="8" t="n">
         <f aca="false">D12</f>
         <v>0</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="8" t="n">
         <f aca="false">E12</f>
         <v>0</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="8" t="n">
         <f aca="false">F12</f>
         <v>0</v>
       </c>
-      <c r="G15" s="9" t="n">
+      <c r="G15" s="8" t="n">
         <f aca="false">G12</f>
         <v>0</v>
       </c>
-      <c r="H15" s="9" t="n">
+      <c r="H15" s="8" t="n">
         <f aca="false">H12</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" s="20" t="str">
+      <c r="B16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="19" t="str">
         <f aca="false">IFERROR(C15/C5,"-")</f>
         <v>-</v>
       </c>
-      <c r="D16" s="20" t="str">
+      <c r="D16" s="19" t="str">
         <f aca="false">IFERROR(D15/D5,"-")</f>
         <v>-</v>
       </c>
-      <c r="E16" s="20" t="str">
+      <c r="E16" s="19" t="str">
         <f aca="false">IFERROR(E15/E5,"-")</f>
         <v>-</v>
       </c>
-      <c r="F16" s="20" t="str">
+      <c r="F16" s="19" t="str">
         <f aca="false">IFERROR(F15/F5,"-")</f>
         <v>-</v>
       </c>
-      <c r="G16" s="20" t="str">
+      <c r="G16" s="19" t="str">
         <f aca="false">IFERROR(G15/G5,"-")</f>
         <v>-</v>
       </c>
-      <c r="H16" s="20" t="str">
+      <c r="H16" s="19" t="str">
         <f aca="false">IFERROR(H15/H5,"-")</f>
         <v>-</v>
       </c>
@@ -1369,132 +1376,132 @@
   <dimension ref="B2:C20"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>52</v>
+      <c r="B2" s="1" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="5" t="s">
-        <v>53</v>
+      <c r="B4" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C5" s="21" t="n">
+      <c r="B5" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" s="22" t="n">
+      <c r="B6" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="21" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" s="9" t="n">
+      <c r="B7" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="8" t="n">
         <f aca="false">C5*C6</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" s="23" t="n">
+      <c r="B8" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="22" t="n">
         <f aca="false">'Sources &amp; Uses'!C9</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="5" t="s">
-        <v>58</v>
+      <c r="B10" s="4" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C11" s="23" t="n">
+      <c r="B11" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="22" t="n">
         <f aca="false">'Debt Schedule'!H5</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12" s="22" t="n">
+      <c r="B12" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="21" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C13" s="9" t="n">
+      <c r="B13" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="8" t="n">
         <f aca="false">C11*C12</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C14" s="23" t="n">
+      <c r="B14" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="22" t="n">
         <f aca="false">'Debt Schedule'!H15</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C15" s="8" t="n">
+      <c r="B15" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="7" t="n">
         <f aca="false">C13-C14</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="5" t="s">
-        <v>64</v>
+      <c r="B17" s="4" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C18" s="24" t="str">
+      <c r="B18" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="23" t="str">
         <f aca="false">IFERROR(C15/C8,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="12" t="n">
-        <f aca="false">Cover!C8</f>
+      <c r="B19" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" s="11" t="n">
+        <f aca="false">Cover!C9</f>
         <v>5</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" s="25" t="str">
+      <c r="B20" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="24" t="str">
         <f aca="false">IFERROR(C18^(1/C19)-1,"-")</f>
         <v>-</v>
       </c>
@@ -1518,134 +1525,134 @@
   <dimension ref="B2:G9"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="12"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>68</v>
+      <c r="B2" s="1" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" s="26" t="n">
+      <c r="B4" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="D4" s="26" t="n">
+      <c r="D4" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="26" t="n">
+      <c r="E4" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="F4" s="26" t="n">
+      <c r="F4" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="G4" s="26" t="n">
+      <c r="G4" s="25" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="26" t="n">
+      <c r="B5" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="C5" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="G5" s="19" t="s">
-        <v>70</v>
+      <c r="C5" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="26" t="n">
+      <c r="B6" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="C6" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="G6" s="19" t="s">
-        <v>70</v>
+      <c r="C6" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="G6" s="18" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="26" t="n">
+      <c r="B7" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="C7" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="G7" s="19" t="s">
-        <v>70</v>
+      <c r="C7" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="26" t="n">
+      <c r="B8" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="C8" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="F8" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="G8" s="19" t="s">
-        <v>70</v>
+      <c r="C8" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" s="18" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="26" t="n">
+      <c r="B9" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="C9" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="G9" s="19" t="s">
-        <v>70</v>
+      <c r="C9" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1667,33 +1674,33 @@
   <dimension ref="B2:F4"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>71</v>
+      <c r="B2" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="E4" s="9" t="s">
         <v>76</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/03_Private_Equity/_template_LBO.xlsx
+++ b/03_Private_Equity/_template_LBO.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="107">
   <si>
     <t xml:space="preserve">[TARGET] — LBO Model</t>
   </si>
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Check (sources = uses):</t>
   </si>
   <si>
-    <t xml:space="preserve">Debt Schedule (with cash sweep)</t>
+    <t xml:space="preserve">Debt Schedule — Revolver / TLA / TLB (with cash sweep)</t>
   </si>
   <si>
     <t xml:space="preserve">Yr0</t>
@@ -141,48 +141,93 @@
     <t xml:space="preserve">Entry EBITDA growth (%/yr)</t>
   </si>
   <si>
-    <t xml:space="preserve">Cash flow available for debt paydown (FCF)</t>
+    <t xml:space="preserve">Cash flow available for debt service (FCF)</t>
   </si>
   <si>
     <t xml:space="preserve">FCF conversion (FCF / EBITDA, %)</t>
   </si>
   <si>
-    <t xml:space="preserve">Mandatory amort (% of original TLB/yr)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cash sweep (% of excess FCF, after debt svc)</t>
+    <t xml:space="preserve">TLA mandatory amort (% of original/yr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revolving Credit Facility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TLA interest rate (%)</t>
   </si>
   <si>
     <t xml:space="preserve">  Beginning balance</t>
   </si>
   <si>
-    <t xml:space="preserve">Term Loan B interest rate (%)</t>
+    <t xml:space="preserve">TLB mandatory amort (% of original/yr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Interest expense (rate x beginning balance)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TLB interest rate (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Cash available for revolver / sweep decisions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash sweep (% of excess cash, after revolver)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Draw / (repayment)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revolver commitment / capacity ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Ending balance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revolver interest rate (%, on drawn balance)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Excess cash remaining for term loan sweep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Original TLA balance (Yr0, $)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Original TLB balance (Yr0, $)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Term Loan A (senior, amortizing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revolver drawn at close ($)</t>
   </si>
   <si>
     <t xml:space="preserve">  Mandatory amortization</t>
   </si>
   <si>
-    <t xml:space="preserve">Original TLB balance (Yr0, $)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Cash sweep (excess FCF after debt svc)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Ending balance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Models Term Loan B only — the amortizing/sweep tranche in a typical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Interest expense (rate x beginning balance)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">structure. Revolver stays undrawn at close; notes are bullet/no-amort.</t>
+    <t xml:space="preserve">Revolver commitment (K12) is total facility SIZE available to draw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Cash sweep (after revolver fully repaid)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">against, separate from Sources &amp; Uses' 'drawn at close' amount (K16),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">which is typically 0 for a fresh LBO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Term Loan B (junior)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Cash sweep (only after TLA fully repaid)</t>
   </si>
   <si>
     <t xml:space="preserve">Total debt (end of period)</t>
   </si>
   <si>
+    <t xml:space="preserve">Total interest expense</t>
+  </si>
+  <si>
     <t xml:space="preserve">Total debt / EBITDA (leverage)</t>
   </si>
   <si>
@@ -222,16 +267,58 @@
     <t xml:space="preserve">Exit equity value</t>
   </si>
   <si>
-    <t xml:space="preserve">Returns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MOIC</t>
+    <t xml:space="preserve">Deal-Level Returns (blended, before management promote)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOIC (exit equity value / ALL invested equity, sponsor + mgmt)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Everyone's return before the promote reallocates value from sponsor to management below — not the sponsor's actual net return</t>
   </si>
   <si>
     <t xml:space="preserve">Hold period (yrs)</t>
   </si>
   <si>
     <t xml:space="preserve">IRR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Management Promote / Ratchet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total sponsor + management invested equity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Management rollover % of total equity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRR hurdle for promote to kick in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Management promote % of value created above hurdle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hurdle equity value (invested equity grown at hurdle IRR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value created above hurdle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Management promote ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Management total proceeds (pro-rata rollover + promote)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sponsor net proceeds (exit equity value less management take)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sponsor-only MOIC (on sponsor equity, net of promote paid away)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sponsor-only IRR (net of promote paid away)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is the number that actually matters to the sponsor's LPs — the blended IRR above overstates what the fund itself earns once management's promote is paid away</t>
   </si>
   <si>
     <t xml:space="preserve">Sensitivity — IRR by Entry/Exit Multiple</t>
@@ -422,7 +509,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -483,11 +570,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -520,6 +611,22 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1006,14 +1113,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:K16"/>
+  <dimension ref="B2:K32"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="14"/>
   </cols>
   <sheetData>
@@ -1121,239 +1228,640 @@
         <v>40</v>
       </c>
       <c r="K7" s="14" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="2" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K8" s="14" t="n">
-        <v>0.75</v>
+        <v>42</v>
+      </c>
+      <c r="K8" s="15" t="n">
+        <v>0.07</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="15" t="n">
-        <f aca="false">$K$10</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="15" t="n">
-        <f aca="false">C12</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="15" t="n">
-        <f aca="false">D12</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="15" t="n">
-        <f aca="false">E12</f>
-        <v>0</v>
-      </c>
-      <c r="G9" s="15" t="n">
-        <f aca="false">F12</f>
-        <v>0</v>
-      </c>
-      <c r="H9" s="15" t="n">
-        <f aca="false">G12</f>
+        <v>43</v>
+      </c>
+      <c r="C9" s="16" t="n">
+        <f aca="false">$K$16</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <f aca="false">C13</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <f aca="false">D13</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <f aca="false">E13</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <f aca="false">F13</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="16" t="n">
+        <f aca="false">G13</f>
         <v>0</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="K9" s="16" t="n">
-        <v>0.09</v>
+        <v>44</v>
+      </c>
+      <c r="K9" s="14" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="15" t="n">
-        <f aca="false">MIN($K$10*$K$7,C9)</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="15" t="n">
-        <f aca="false">MIN($K$10*$K$7,D9)</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <f aca="false">MIN($K$10*$K$7,E9)</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="15" t="n">
-        <f aca="false">MIN($K$10*$K$7,F9)</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="15" t="n">
-        <f aca="false">MIN($K$10*$K$7,G9)</f>
-        <v>0</v>
-      </c>
-      <c r="H10" s="15" t="n">
-        <f aca="false">MIN($K$10*$K$7,H9)</f>
-        <v>0</v>
-      </c>
-      <c r="J10" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="K10" s="12" t="n">
-        <f aca="false">'Sources &amp; Uses'!C7</f>
-        <v>0</v>
+      <c r="C10" s="16" t="n">
+        <f aca="false">C9*$K$13</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="16" t="n">
+        <f aca="false">D9*$K$13</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <f aca="false">E9*$K$13</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="16" t="n">
+        <f aca="false">F9*$K$13</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="16" t="n">
+        <f aca="false">G9*$K$13</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="16" t="n">
+        <f aca="false">H9*$K$13</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="K10" s="15" t="n">
+        <v>0.095</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="15" t="n">
-        <f aca="false">MIN(MAX(0,$K$8*(C6-C10-C13)),C9-C10)</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="15" t="n">
-        <f aca="false">MIN(MAX(0,$K$8*(D6-D10-D13)),D9-D10)</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <f aca="false">MIN(MAX(0,$K$8*(E6-E10-E13)),E9-E10)</f>
-        <v>0</v>
-      </c>
-      <c r="F11" s="15" t="n">
-        <f aca="false">MIN(MAX(0,$K$8*(F6-F10-F13)),F9-F10)</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="15" t="n">
-        <f aca="false">MIN(MAX(0,$K$8*(G6-G10-G13)),G9-G10)</f>
-        <v>0</v>
-      </c>
-      <c r="H11" s="15" t="n">
-        <f aca="false">MIN(MAX(0,$K$8*(H6-H10-H13)),H9-H10)</f>
-        <v>0</v>
+        <v>47</v>
+      </c>
+      <c r="C11" s="16" t="n">
+        <f aca="false">C6-C18-C25-C10-C21-C28</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <f aca="false">D6-D18-D25-D10-D21-D28</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <f aca="false">E6-E18-E25-E10-E21-E28</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <f aca="false">F6-F18-F25-F10-F21-F28</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <f aca="false">G6-G18-G25-G10-G21-G28</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="16" t="n">
+        <f aca="false">H6-H18-H25-H10-H21-H28</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="K11" s="14" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" s="15" t="n">
-        <f aca="false">C9-C10-C11</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="15" t="n">
-        <f aca="false">D9-D10-D11</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <f aca="false">E9-E10-E11</f>
-        <v>0</v>
-      </c>
-      <c r="F12" s="15" t="n">
-        <f aca="false">F9-F10-F11</f>
-        <v>0</v>
-      </c>
-      <c r="G12" s="15" t="n">
-        <f aca="false">G9-G10-G11</f>
-        <v>0</v>
-      </c>
-      <c r="H12" s="15" t="n">
-        <f aca="false">H9-H10-H11</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="18" t="s">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="C12" s="16" t="n">
+        <f aca="false">IF(C11&lt;0,MIN(-C11,$K$12-C9),-MIN(C9,MAX(0,C11)))</f>
+        <v>-0</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <f aca="false">IF(D11&lt;0,MIN(-D11,$K$12-D9),-MIN(D9,MAX(0,D11)))</f>
+        <v>-0</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <f aca="false">IF(E11&lt;0,MIN(-E11,$K$12-E9),-MIN(E9,MAX(0,E11)))</f>
+        <v>-0</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <f aca="false">IF(F11&lt;0,MIN(-F11,$K$12-F9),-MIN(F9,MAX(0,F11)))</f>
+        <v>-0</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <f aca="false">IF(G11&lt;0,MIN(-G11,$K$12-G9),-MIN(G9,MAX(0,G11)))</f>
+        <v>-0</v>
+      </c>
+      <c r="H12" s="16" t="n">
+        <f aca="false">IF(H11&lt;0,MIN(-H11,$K$12-H9),-MIN(H9,MAX(0,H11)))</f>
+        <v>-0</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K12" s="17" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13" s="15" t="n">
-        <f aca="false">C9*$K$9</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="15" t="n">
-        <f aca="false">D9*$K$9</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="15" t="n">
-        <f aca="false">E9*$K$9</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="15" t="n">
-        <f aca="false">F9*$K$9</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="15" t="n">
-        <f aca="false">G9*$K$9</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="15" t="n">
-        <f aca="false">H9*$K$9</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="18" t="s">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="C13" s="16" t="n">
+        <f aca="false">C9+C12</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <f aca="false">D9+D12</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <f aca="false">E9+E12</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <f aca="false">F9+F12</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <f aca="false">G9+G12</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="16" t="n">
+        <f aca="false">H9+H12</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K13" s="15" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="16" t="n">
+        <f aca="false">MAX(0,MAX(0,C11)-C9)</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="16" t="n">
+        <f aca="false">MAX(0,MAX(0,D11)-D9)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <f aca="false">MAX(0,MAX(0,E11)-E9)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="16" t="n">
+        <f aca="false">MAX(0,MAX(0,F11)-F9)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="16" t="n">
+        <f aca="false">MAX(0,MAX(0,G11)-G9)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="16" t="n">
+        <f aca="false">MAX(0,MAX(0,H11)-H9)</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="K14" s="12" t="n">
+        <f aca="false">'Sources &amp; Uses'!C6</f>
+        <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" s="8" t="n">
-        <f aca="false">C12</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="8" t="n">
-        <f aca="false">D12</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <f aca="false">E12</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="8" t="n">
-        <f aca="false">F12</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="8" t="n">
-        <f aca="false">G12</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="8" t="n">
-        <f aca="false">H12</f>
+      <c r="J15" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="K15" s="12" t="n">
+        <f aca="false">'Sources &amp; Uses'!C7</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" s="19" t="str">
-        <f aca="false">IFERROR(C15/C5,"-")</f>
+        <v>56</v>
+      </c>
+      <c r="J16" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="K16" s="12" t="n">
+        <f aca="false">'Sources &amp; Uses'!C5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="16" t="n">
+        <f aca="false">$K$14</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="16" t="n">
+        <f aca="false">C20</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <f aca="false">D20</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="16" t="n">
+        <f aca="false">E20</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="16" t="n">
+        <f aca="false">F20</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="16" t="n">
+        <f aca="false">G20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" s="16" t="n">
+        <f aca="false">MIN($K$14*$K$7,C17)</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="16" t="n">
+        <f aca="false">MIN($K$14*$K$7,D17)</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="16" t="n">
+        <f aca="false">MIN($K$14*$K$7,E17)</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="16" t="n">
+        <f aca="false">MIN($K$14*$K$7,F17)</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="16" t="n">
+        <f aca="false">MIN($K$14*$K$7,G17)</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="16" t="n">
+        <f aca="false">MIN($K$14*$K$7,H17)</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="16" t="n">
+        <f aca="false">MIN($K$11*C14,C17-C18)</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="16" t="n">
+        <f aca="false">MIN($K$11*D14,D17-D18)</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <f aca="false">MIN($K$11*E14,E17-E18)</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="16" t="n">
+        <f aca="false">MIN($K$11*F14,F17-F18)</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="16" t="n">
+        <f aca="false">MIN($K$11*G14,G17-G18)</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="16" t="n">
+        <f aca="false">MIN($K$11*H14,H17-H18)</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="19" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="16" t="n">
+        <f aca="false">C17-C18-C19</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="16" t="n">
+        <f aca="false">D17-D18-D19</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="16" t="n">
+        <f aca="false">E17-E18-E19</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="16" t="n">
+        <f aca="false">F17-F18-F19</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="16" t="n">
+        <f aca="false">G17-G18-G19</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="16" t="n">
+        <f aca="false">H17-H18-H19</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="16" t="n">
+        <f aca="false">C17*$K$8</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="16" t="n">
+        <f aca="false">D17*$K$8</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="16" t="n">
+        <f aca="false">E17*$K$8</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="16" t="n">
+        <f aca="false">F17*$K$8</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="16" t="n">
+        <f aca="false">G17*$K$8</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="16" t="n">
+        <f aca="false">H17*$K$8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" s="16" t="n">
+        <f aca="false">$K$15</f>
+        <v>0</v>
+      </c>
+      <c r="D24" s="16" t="n">
+        <f aca="false">C27</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="16" t="n">
+        <f aca="false">D27</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="16" t="n">
+        <f aca="false">E27</f>
+        <v>0</v>
+      </c>
+      <c r="G24" s="16" t="n">
+        <f aca="false">F27</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="16" t="n">
+        <f aca="false">G27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" s="16" t="n">
+        <f aca="false">MIN($K$15*$K$9,C24)</f>
+        <v>0</v>
+      </c>
+      <c r="D25" s="16" t="n">
+        <f aca="false">MIN($K$15*$K$9,D24)</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="16" t="n">
+        <f aca="false">MIN($K$15*$K$9,E24)</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="16" t="n">
+        <f aca="false">MIN($K$15*$K$9,F24)</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="16" t="n">
+        <f aca="false">MIN($K$15*$K$9,G24)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="16" t="n">
+        <f aca="false">MIN($K$15*$K$9,H24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="C26" s="16" t="n">
+        <f aca="false">MIN($K$11*C14-C19,C24-C25)</f>
+        <v>0</v>
+      </c>
+      <c r="D26" s="16" t="n">
+        <f aca="false">MIN($K$11*D14-D19,D24-D25)</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <f aca="false">MIN($K$11*E14-E19,E24-E25)</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="16" t="n">
+        <f aca="false">MIN($K$11*F14-F19,F24-F25)</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="16" t="n">
+        <f aca="false">MIN($K$11*G14-G19,G24-G25)</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="16" t="n">
+        <f aca="false">MIN($K$11*H14-H19,H24-H25)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="16" t="n">
+        <f aca="false">C24-C25-C26</f>
+        <v>0</v>
+      </c>
+      <c r="D27" s="16" t="n">
+        <f aca="false">D24-D25-D26</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="16" t="n">
+        <f aca="false">E24-E25-E26</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="16" t="n">
+        <f aca="false">F24-F25-F26</f>
+        <v>0</v>
+      </c>
+      <c r="G27" s="16" t="n">
+        <f aca="false">G24-G25-G26</f>
+        <v>0</v>
+      </c>
+      <c r="H27" s="16" t="n">
+        <f aca="false">H24-H25-H26</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" s="16" t="n">
+        <f aca="false">C24*$K$10</f>
+        <v>0</v>
+      </c>
+      <c r="D28" s="16" t="n">
+        <f aca="false">D24*$K$10</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="16" t="n">
+        <f aca="false">E24*$K$10</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="16" t="n">
+        <f aca="false">F24*$K$10</f>
+        <v>0</v>
+      </c>
+      <c r="G28" s="16" t="n">
+        <f aca="false">G24*$K$10</f>
+        <v>0</v>
+      </c>
+      <c r="H28" s="16" t="n">
+        <f aca="false">H24*$K$10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" s="8" t="n">
+        <f aca="false">C13+C20+C27</f>
+        <v>0</v>
+      </c>
+      <c r="D30" s="8" t="n">
+        <f aca="false">D13+D20+D27</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <f aca="false">E13+E20+E27</f>
+        <v>0</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <f aca="false">F13+F20+F27</f>
+        <v>0</v>
+      </c>
+      <c r="G30" s="8" t="n">
+        <f aca="false">G13+G20+G27</f>
+        <v>0</v>
+      </c>
+      <c r="H30" s="8" t="n">
+        <f aca="false">H13+H20+H27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C31" s="8" t="n">
+        <f aca="false">C10+C21+C28</f>
+        <v>0</v>
+      </c>
+      <c r="D31" s="8" t="n">
+        <f aca="false">D10+D21+D28</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <f aca="false">E10+E21+E28</f>
+        <v>0</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <f aca="false">F10+F21+F28</f>
+        <v>0</v>
+      </c>
+      <c r="G31" s="8" t="n">
+        <f aca="false">G10+G21+G28</f>
+        <v>0</v>
+      </c>
+      <c r="H31" s="8" t="n">
+        <f aca="false">H10+H21+H28</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32" s="20" t="str">
+        <f aca="false">IFERROR(C30/C5,"-")</f>
         <v>-</v>
       </c>
-      <c r="D16" s="19" t="str">
-        <f aca="false">IFERROR(D15/D5,"-")</f>
+      <c r="D32" s="20" t="str">
+        <f aca="false">IFERROR(D30/D5,"-")</f>
         <v>-</v>
       </c>
-      <c r="E16" s="19" t="str">
-        <f aca="false">IFERROR(E15/E5,"-")</f>
+      <c r="E32" s="20" t="str">
+        <f aca="false">IFERROR(E30/E5,"-")</f>
         <v>-</v>
       </c>
-      <c r="F16" s="19" t="str">
-        <f aca="false">IFERROR(F15/F5,"-")</f>
+      <c r="F32" s="20" t="str">
+        <f aca="false">IFERROR(F30/F5,"-")</f>
         <v>-</v>
       </c>
-      <c r="G16" s="19" t="str">
-        <f aca="false">IFERROR(G15/G5,"-")</f>
+      <c r="G32" s="20" t="str">
+        <f aca="false">IFERROR(G30/G5,"-")</f>
         <v>-</v>
       </c>
-      <c r="H16" s="19" t="str">
-        <f aca="false">IFERROR(H15/H5,"-")</f>
+      <c r="H32" s="20" t="str">
+        <f aca="false">IFERROR(H30/H5,"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -1373,7 +1881,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:C20"/>
+  <dimension ref="B2:D33"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -1383,33 +1891,33 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="4" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="C5" s="21" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="21" t="n">
+        <v>71</v>
+      </c>
+      <c r="C6" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="C7" s="8" t="n">
         <f aca="false">C5*C6</f>
@@ -1418,38 +1926,38 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="C8" s="22" t="n">
+        <v>73</v>
+      </c>
+      <c r="C8" s="23" t="n">
         <f aca="false">'Sources &amp; Uses'!C9</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="4" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" s="22" t="n">
+        <v>75</v>
+      </c>
+      <c r="C11" s="23" t="n">
         <f aca="false">'Debt Schedule'!H5</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="C12" s="21" t="n">
+        <v>76</v>
+      </c>
+      <c r="C12" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="0" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="C13" s="8" t="n">
         <f aca="false">C11*C12</f>
@@ -1458,16 +1966,16 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="C14" s="22" t="n">
-        <f aca="false">'Debt Schedule'!H15</f>
+        <v>78</v>
+      </c>
+      <c r="C14" s="23" t="n">
+        <f aca="false">'Debt Schedule'!H30</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="0" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="C15" s="7" t="n">
         <f aca="false">C13-C14</f>
@@ -1476,21 +1984,24 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" s="23" t="str">
-        <f aca="false">IFERROR(C15/C8,"-")</f>
+        <v>81</v>
+      </c>
+      <c r="C18" s="24" t="str">
+        <f aca="false">IFERROR(C15/(C8+'Sources &amp; Uses'!C10),"-")</f>
         <v>-</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="0" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="C19" s="11" t="n">
         <f aca="false">Cover!C9</f>
@@ -1499,11 +2010,116 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="C20" s="24" t="str">
+        <v>84</v>
+      </c>
+      <c r="C20" s="25" t="str">
         <f aca="false">IFERROR(C18^(1/C19)-1,"-")</f>
         <v>-</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="C23" s="12" t="n">
+        <f aca="false">'Sources &amp; Uses'!C9+'Sources &amp; Uses'!C10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="C24" s="26" t="str">
+        <f aca="false">IFERROR('Sources &amp; Uses'!C10/C23,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="C26" s="14" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="C27" s="13" t="n">
+        <f aca="false">IFERROR(C23*(1+C25)^C19,"-")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="C28" s="13" t="n">
+        <f aca="false">MAX(0,C15-C27)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="C29" s="27" t="n">
+        <f aca="false">C28*C26</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" s="27" t="str">
+        <f aca="false">IFERROR(C24*C15+C29,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" s="27" t="str">
+        <f aca="false">IFERROR(C15-C30,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="C32" s="28" t="str">
+        <f aca="false">IFERROR(C31/'Sources &amp; Uses'!C9,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="C33" s="29" t="str">
+        <f aca="false">IFERROR(C32^(1/C19)-1,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D33" s="19" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1532,127 +2148,127 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" s="25" t="n">
+        <v>99</v>
+      </c>
+      <c r="C4" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="D4" s="25" t="n">
+      <c r="D4" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="25" t="n">
+      <c r="E4" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="F4" s="25" t="n">
+      <c r="F4" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="G4" s="25" t="n">
+      <c r="G4" s="30" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="25" t="n">
+      <c r="B5" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="C5" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>71</v>
+      <c r="C5" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="25" t="n">
+      <c r="B6" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="C6" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="F6" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>71</v>
+      <c r="C6" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="25" t="n">
+      <c r="B7" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="C7" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>71</v>
+      <c r="C7" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="25" t="n">
+      <c r="B8" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="C8" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>71</v>
+      <c r="C8" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="25" t="n">
+      <c r="B9" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="C9" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>71</v>
+      <c r="C9" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1683,24 +2299,24 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="9" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/03_Private_Equity/_template_LBO.xlsx
+++ b/03_Private_Equity/_template_LBO.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="112">
   <si>
     <t xml:space="preserve">[TARGET] — LBO Model</t>
   </si>
@@ -60,6 +60,12 @@
     <t xml:space="preserve">Weekly</t>
   </si>
   <si>
+    <t xml:space="preserve">Active scenario (Base or Downside):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sources &amp; Uses</t>
   </si>
   <si>
@@ -135,6 +141,12 @@
     <t xml:space="preserve">Assumptions</t>
   </si>
   <si>
+    <t xml:space="preserve">Downside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active</t>
+  </si>
+  <si>
     <t xml:space="preserve">EBITDA</t>
   </si>
   <si>
@@ -204,16 +216,19 @@
     <t xml:space="preserve">  Mandatory amortization</t>
   </si>
   <si>
-    <t xml:space="preserve">Revolver commitment (K12) is total facility SIZE available to draw</t>
+    <t xml:space="preserve">Deal terms (rows 14-16) don't vary by scenario, so they skip the</t>
   </si>
   <si>
     <t xml:space="preserve">  Cash sweep (after revolver fully repaid)</t>
   </si>
   <si>
-    <t xml:space="preserve">against, separate from Sources &amp; Uses' 'drawn at close' amount (K16),</t>
-  </si>
-  <si>
-    <t xml:space="preserve">which is typically 0 for a fresh LBO.</t>
+    <t xml:space="preserve">Base/Downside split and go straight in the Active column. Revolver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commitment (M12) is total facility SIZE available to draw against,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">separate from the 'drawn at close' amount (M16, typically 0).</t>
   </si>
   <si>
     <t xml:space="preserve">Term Loan B (junior)</t>
@@ -255,7 +270,7 @@
     <t xml:space="preserve">Exit EBITDA (Yr5)</t>
   </si>
   <si>
-    <t xml:space="preserve">Exit multiple</t>
+    <t xml:space="preserve">Exit multiple (Active)</t>
   </si>
   <si>
     <t xml:space="preserve">Exit EV</t>
@@ -509,7 +524,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -550,10 +565,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -570,10 +581,18 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="167" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -606,15 +625,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="168" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -886,7 +905,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:C10"/>
+  <dimension ref="B2:C11"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -952,6 +971,14 @@
       </c>
       <c r="C10" s="3" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -983,26 +1010,26 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>0</v>
@@ -1010,13 +1037,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>0</v>
@@ -1024,13 +1051,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>0</v>
@@ -1038,13 +1065,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>0</v>
@@ -1052,13 +1079,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>0</v>
@@ -1066,13 +1093,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F10" s="7" t="n">
         <f aca="false">SUM(F5:F9)</f>
@@ -1081,7 +1108,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C11" s="7" t="n">
         <f aca="false">SUM(C5:C10)</f>
@@ -1090,7 +1117,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C13" s="8" t="n">
         <f aca="false">C11-F10</f>
@@ -1113,674 +1140,749 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:K32"/>
+  <dimension ref="B2:M32"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4" s="9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="K4" s="10"/>
+        <v>37</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="12" t="n">
+      <c r="B5" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="11" t="n">
         <f aca="false">Returns!C5</f>
         <v>0</v>
       </c>
-      <c r="D5" s="13" t="n">
-        <f aca="false">C5*(1+$K$5)</f>
-        <v>0</v>
-      </c>
-      <c r="E5" s="13" t="n">
-        <f aca="false">D5*(1+$K$5)</f>
-        <v>0</v>
-      </c>
-      <c r="F5" s="13" t="n">
-        <f aca="false">E5*(1+$K$5)</f>
-        <v>0</v>
-      </c>
-      <c r="G5" s="13" t="n">
-        <f aca="false">F5*(1+$K$5)</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="13" t="n">
-        <f aca="false">G5*(1+$K$5)</f>
+      <c r="D5" s="12" t="n">
+        <f aca="false">C5*(1+$M$5)</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <f aca="false">D5*(1+$M$5)</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <f aca="false">E5*(1+$M$5)</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <f aca="false">F5*(1+$M$5)</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="12" t="n">
+        <f aca="false">G5*(1+$M$5)</f>
         <v>0</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="K5" s="14" t="n">
+        <v>41</v>
+      </c>
+      <c r="K5" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L5" s="13" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="M5" s="14" t="n">
+        <f aca="false">IF(Cover!$C$11="Downside",L5,K5)</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="13" t="n">
-        <f aca="false">C5*$K$6</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="13" t="n">
-        <f aca="false">D5*$K$6</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="13" t="n">
-        <f aca="false">E5*$K$6</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="13" t="n">
-        <f aca="false">F5*$K$6</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="13" t="n">
-        <f aca="false">G5*$K$6</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="13" t="n">
-        <f aca="false">H5*$K$6</f>
+        <v>42</v>
+      </c>
+      <c r="C6" s="12" t="n">
+        <f aca="false">C5*$M$6</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <f aca="false">D5*$M$6</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <f aca="false">E5*$M$6</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <f aca="false">F5*$M$6</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <f aca="false">G5*$M$6</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="12" t="n">
+        <f aca="false">H5*$M$6</f>
         <v>0</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="K6" s="14" t="n">
+        <v>43</v>
+      </c>
+      <c r="K6" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L6" s="13" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M6" s="14" t="n">
+        <f aca="false">IF(Cover!$C$11="Downside",L6,K6)</f>
         <v>0.5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="K7" s="14" t="n">
+        <v>44</v>
+      </c>
+      <c r="K7" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L7" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M7" s="14" t="n">
+        <f aca="false">IF(Cover!$C$11="Downside",L7,K7)</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K8" s="15" t="n">
         <v>0.07</v>
       </c>
+      <c r="L8" s="15" t="n">
+        <v>0.085</v>
+      </c>
+      <c r="M8" s="16" t="n">
+        <f aca="false">IF(Cover!$C$11="Downside",L8,K8)</f>
+        <v>0.07</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="16" t="n">
-        <f aca="false">$K$16</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="16" t="n">
+        <v>47</v>
+      </c>
+      <c r="C9" s="17" t="n">
+        <f aca="false">$M$16</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="17" t="n">
         <f aca="false">C13</f>
         <v>0</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <f aca="false">D13</f>
         <v>0</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="17" t="n">
         <f aca="false">E13</f>
         <v>0</v>
       </c>
-      <c r="G9" s="16" t="n">
+      <c r="G9" s="17" t="n">
         <f aca="false">F13</f>
         <v>0</v>
       </c>
-      <c r="H9" s="16" t="n">
+      <c r="H9" s="17" t="n">
         <f aca="false">G13</f>
         <v>0</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="K9" s="14" t="n">
+        <v>48</v>
+      </c>
+      <c r="K9" s="13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L9" s="13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M9" s="14" t="n">
+        <f aca="false">IF(Cover!$C$11="Downside",L9,K9)</f>
         <v>0.01</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="16" t="n">
-        <f aca="false">C9*$K$13</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="16" t="n">
-        <f aca="false">D9*$K$13</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <f aca="false">E9*$K$13</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <f aca="false">F9*$K$13</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="16" t="n">
-        <f aca="false">G9*$K$13</f>
-        <v>0</v>
-      </c>
-      <c r="H10" s="16" t="n">
-        <f aca="false">H9*$K$13</f>
+        <v>49</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <f aca="false">C9*$M$13</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <f aca="false">D9*$M$13</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <f aca="false">E9*$M$13</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="17" t="n">
+        <f aca="false">F9*$M$13</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="17" t="n">
+        <f aca="false">G9*$M$13</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <f aca="false">H9*$M$13</f>
         <v>0</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K10" s="15" t="n">
         <v>0.095</v>
       </c>
+      <c r="L10" s="15" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="M10" s="16" t="n">
+        <f aca="false">IF(Cover!$C$11="Downside",L10,K10)</f>
+        <v>0.095</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" s="16" t="n">
+        <v>51</v>
+      </c>
+      <c r="C11" s="17" t="n">
         <f aca="false">C6-C18-C25-C10-C21-C28</f>
         <v>0</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <f aca="false">D6-D18-D25-D10-D21-D28</f>
         <v>0</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <f aca="false">E6-E18-E25-E10-E21-E28</f>
         <v>0</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="17" t="n">
         <f aca="false">F6-F18-F25-F10-F21-F28</f>
         <v>0</v>
       </c>
-      <c r="G11" s="16" t="n">
+      <c r="G11" s="17" t="n">
         <f aca="false">G6-G18-G25-G10-G21-G28</f>
         <v>0</v>
       </c>
-      <c r="H11" s="16" t="n">
+      <c r="H11" s="17" t="n">
         <f aca="false">H6-H18-H25-H10-H21-H28</f>
         <v>0</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="K11" s="14" t="n">
+        <v>52</v>
+      </c>
+      <c r="K11" s="13" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L11" s="13" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M11" s="14" t="n">
+        <f aca="false">IF(Cover!$C$11="Downside",L11,K11)</f>
         <v>0.75</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" s="16" t="n">
-        <f aca="false">IF(C11&lt;0,MIN(-C11,$K$12-C9),-MIN(C9,MAX(0,C11)))</f>
+        <v>53</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <f aca="false">IF(C11&lt;0,MIN(-C11,$M$12-C9),-MIN(C9,MAX(0,C11)))</f>
         <v>-0</v>
       </c>
-      <c r="D12" s="16" t="n">
-        <f aca="false">IF(D11&lt;0,MIN(-D11,$K$12-D9),-MIN(D9,MAX(0,D11)))</f>
+      <c r="D12" s="17" t="n">
+        <f aca="false">IF(D11&lt;0,MIN(-D11,$M$12-D9),-MIN(D9,MAX(0,D11)))</f>
         <v>-0</v>
       </c>
-      <c r="E12" s="16" t="n">
-        <f aca="false">IF(E11&lt;0,MIN(-E11,$K$12-E9),-MIN(E9,MAX(0,E11)))</f>
+      <c r="E12" s="17" t="n">
+        <f aca="false">IF(E11&lt;0,MIN(-E11,$M$12-E9),-MIN(E9,MAX(0,E11)))</f>
         <v>-0</v>
       </c>
-      <c r="F12" s="16" t="n">
-        <f aca="false">IF(F11&lt;0,MIN(-F11,$K$12-F9),-MIN(F9,MAX(0,F11)))</f>
+      <c r="F12" s="17" t="n">
+        <f aca="false">IF(F11&lt;0,MIN(-F11,$M$12-F9),-MIN(F9,MAX(0,F11)))</f>
         <v>-0</v>
       </c>
-      <c r="G12" s="16" t="n">
-        <f aca="false">IF(G11&lt;0,MIN(-G11,$K$12-G9),-MIN(G9,MAX(0,G11)))</f>
+      <c r="G12" s="17" t="n">
+        <f aca="false">IF(G11&lt;0,MIN(-G11,$M$12-G9),-MIN(G9,MAX(0,G11)))</f>
         <v>-0</v>
       </c>
-      <c r="H12" s="16" t="n">
-        <f aca="false">IF(H11&lt;0,MIN(-H11,$K$12-H9),-MIN(H9,MAX(0,H11)))</f>
+      <c r="H12" s="17" t="n">
+        <f aca="false">IF(H11&lt;0,MIN(-H11,$M$12-H9),-MIN(H9,MAX(0,H11)))</f>
         <v>-0</v>
       </c>
       <c r="J12" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="K12" s="18" t="n">
         <v>50</v>
       </c>
-      <c r="K12" s="17" t="n">
+      <c r="L12" s="18" t="n">
+        <v>50</v>
+      </c>
+      <c r="M12" s="11" t="n">
+        <f aca="false">IF(Cover!$C$11="Downside",L12,K12)</f>
         <v>50</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="16" t="n">
+        <v>55</v>
+      </c>
+      <c r="C13" s="17" t="n">
         <f aca="false">C9+C12</f>
         <v>0</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <f aca="false">D9+D12</f>
         <v>0</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <f aca="false">E9+E12</f>
         <v>0</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="17" t="n">
         <f aca="false">F9+F12</f>
         <v>0</v>
       </c>
-      <c r="G13" s="16" t="n">
+      <c r="G13" s="17" t="n">
         <f aca="false">G9+G12</f>
         <v>0</v>
       </c>
-      <c r="H13" s="16" t="n">
+      <c r="H13" s="17" t="n">
         <f aca="false">H9+H12</f>
         <v>0</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K13" s="15" t="n">
         <v>0.08</v>
       </c>
+      <c r="L13" s="15" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="M13" s="16" t="n">
+        <f aca="false">IF(Cover!$C$11="Downside",L13,K13)</f>
+        <v>0.08</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" s="16" t="n">
+        <v>57</v>
+      </c>
+      <c r="C14" s="17" t="n">
         <f aca="false">MAX(0,MAX(0,C11)-C9)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <f aca="false">MAX(0,MAX(0,D11)-D9)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <f aca="false">MAX(0,MAX(0,E11)-E9)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="17" t="n">
         <f aca="false">MAX(0,MAX(0,F11)-F9)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="16" t="n">
+      <c r="G14" s="17" t="n">
         <f aca="false">MAX(0,MAX(0,G11)-G9)</f>
         <v>0</v>
       </c>
-      <c r="H14" s="16" t="n">
+      <c r="H14" s="17" t="n">
         <f aca="false">MAX(0,MAX(0,H11)-H9)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="K14" s="12" t="n">
+      <c r="J14" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="M14" s="11" t="n">
         <f aca="false">'Sources &amp; Uses'!C6</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J15" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="K15" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="M15" s="11" t="n">
         <f aca="false">'Sources &amp; Uses'!C7</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="J16" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="K16" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="J16" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="M16" s="11" t="n">
         <f aca="false">'Sources &amp; Uses'!C5</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" s="16" t="n">
-        <f aca="false">$K$14</f>
-        <v>0</v>
-      </c>
-      <c r="D17" s="16" t="n">
+        <v>47</v>
+      </c>
+      <c r="C17" s="17" t="n">
+        <f aca="false">$M$14</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="17" t="n">
         <f aca="false">C20</f>
         <v>0</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <f aca="false">D20</f>
         <v>0</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="F17" s="17" t="n">
         <f aca="false">E20</f>
         <v>0</v>
       </c>
-      <c r="G17" s="16" t="n">
+      <c r="G17" s="17" t="n">
         <f aca="false">F20</f>
         <v>0</v>
       </c>
-      <c r="H17" s="16" t="n">
+      <c r="H17" s="17" t="n">
         <f aca="false">G20</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="C18" s="16" t="n">
-        <f aca="false">MIN($K$14*$K$7,C17)</f>
-        <v>0</v>
-      </c>
-      <c r="D18" s="16" t="n">
-        <f aca="false">MIN($K$14*$K$7,D17)</f>
-        <v>0</v>
-      </c>
-      <c r="E18" s="16" t="n">
-        <f aca="false">MIN($K$14*$K$7,E17)</f>
-        <v>0</v>
-      </c>
-      <c r="F18" s="16" t="n">
-        <f aca="false">MIN($K$14*$K$7,F17)</f>
-        <v>0</v>
-      </c>
-      <c r="G18" s="16" t="n">
-        <f aca="false">MIN($K$14*$K$7,G17)</f>
-        <v>0</v>
-      </c>
-      <c r="H18" s="16" t="n">
-        <f aca="false">MIN($K$14*$K$7,H17)</f>
-        <v>0</v>
-      </c>
-      <c r="J18" s="19" t="s">
-        <v>59</v>
+        <v>62</v>
+      </c>
+      <c r="C18" s="17" t="n">
+        <f aca="false">MIN($M$14*$M$7,C17)</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="17" t="n">
+        <f aca="false">MIN($M$14*$M$7,D17)</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <f aca="false">MIN($M$14*$M$7,E17)</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="17" t="n">
+        <f aca="false">MIN($M$14*$M$7,F17)</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="17" t="n">
+        <f aca="false">MIN($M$14*$M$7,G17)</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="17" t="n">
+        <f aca="false">MIN($M$14*$M$7,H17)</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="20" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="C19" s="16" t="n">
-        <f aca="false">MIN($K$11*C14,C17-C18)</f>
-        <v>0</v>
-      </c>
-      <c r="D19" s="16" t="n">
-        <f aca="false">MIN($K$11*D14,D17-D18)</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="16" t="n">
-        <f aca="false">MIN($K$11*E14,E17-E18)</f>
-        <v>0</v>
-      </c>
-      <c r="F19" s="16" t="n">
-        <f aca="false">MIN($K$11*F14,F17-F18)</f>
-        <v>0</v>
-      </c>
-      <c r="G19" s="16" t="n">
-        <f aca="false">MIN($K$11*G14,G17-G18)</f>
-        <v>0</v>
-      </c>
-      <c r="H19" s="16" t="n">
-        <f aca="false">MIN($K$11*H14,H17-H18)</f>
-        <v>0</v>
-      </c>
-      <c r="J19" s="19" t="s">
-        <v>61</v>
+        <v>64</v>
+      </c>
+      <c r="C19" s="17" t="n">
+        <f aca="false">MIN($M$11*C14,C17-C18)</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <f aca="false">MIN($M$11*D14,D17-D18)</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <f aca="false">MIN($M$11*E14,E17-E18)</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="17" t="n">
+        <f aca="false">MIN($M$11*F14,F17-F18)</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="17" t="n">
+        <f aca="false">MIN($M$11*G14,G17-G18)</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="17" t="n">
+        <f aca="false">MIN($M$11*H14,H17-H18)</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="20" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="16" t="n">
+        <v>55</v>
+      </c>
+      <c r="C20" s="17" t="n">
         <f aca="false">C17-C18-C19</f>
         <v>0</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="17" t="n">
         <f aca="false">D17-D18-D19</f>
         <v>0</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="17" t="n">
         <f aca="false">E17-E18-E19</f>
         <v>0</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="F20" s="17" t="n">
         <f aca="false">F17-F18-F19</f>
         <v>0</v>
       </c>
-      <c r="G20" s="16" t="n">
+      <c r="G20" s="17" t="n">
         <f aca="false">G17-G18-G19</f>
         <v>0</v>
       </c>
-      <c r="H20" s="16" t="n">
+      <c r="H20" s="17" t="n">
         <f aca="false">H17-H18-H19</f>
         <v>0</v>
       </c>
-      <c r="J20" s="19" t="s">
-        <v>62</v>
+      <c r="J20" s="20" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="C21" s="16" t="n">
-        <f aca="false">C17*$K$8</f>
-        <v>0</v>
-      </c>
-      <c r="D21" s="16" t="n">
-        <f aca="false">D17*$K$8</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="16" t="n">
-        <f aca="false">E17*$K$8</f>
-        <v>0</v>
-      </c>
-      <c r="F21" s="16" t="n">
-        <f aca="false">F17*$K$8</f>
-        <v>0</v>
-      </c>
-      <c r="G21" s="16" t="n">
-        <f aca="false">G17*$K$8</f>
-        <v>0</v>
-      </c>
-      <c r="H21" s="16" t="n">
-        <f aca="false">H17*$K$8</f>
-        <v>0</v>
+        <v>49</v>
+      </c>
+      <c r="C21" s="17" t="n">
+        <f aca="false">C17*$M$8</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="17" t="n">
+        <f aca="false">D17*$M$8</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <f aca="false">E17*$M$8</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="17" t="n">
+        <f aca="false">F17*$M$8</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="17" t="n">
+        <f aca="false">G17*$M$8</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="17" t="n">
+        <f aca="false">H17*$M$8</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="20" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24" s="16" t="n">
-        <f aca="false">$K$15</f>
-        <v>0</v>
-      </c>
-      <c r="D24" s="16" t="n">
+        <v>47</v>
+      </c>
+      <c r="C24" s="17" t="n">
+        <f aca="false">$M$15</f>
+        <v>0</v>
+      </c>
+      <c r="D24" s="17" t="n">
         <f aca="false">C27</f>
         <v>0</v>
       </c>
-      <c r="E24" s="16" t="n">
+      <c r="E24" s="17" t="n">
         <f aca="false">D27</f>
         <v>0</v>
       </c>
-      <c r="F24" s="16" t="n">
+      <c r="F24" s="17" t="n">
         <f aca="false">E27</f>
         <v>0</v>
       </c>
-      <c r="G24" s="16" t="n">
+      <c r="G24" s="17" t="n">
         <f aca="false">F27</f>
         <v>0</v>
       </c>
-      <c r="H24" s="16" t="n">
+      <c r="H24" s="17" t="n">
         <f aca="false">G27</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="C25" s="16" t="n">
-        <f aca="false">MIN($K$15*$K$9,C24)</f>
-        <v>0</v>
-      </c>
-      <c r="D25" s="16" t="n">
-        <f aca="false">MIN($K$15*$K$9,D24)</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="16" t="n">
-        <f aca="false">MIN($K$15*$K$9,E24)</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="16" t="n">
-        <f aca="false">MIN($K$15*$K$9,F24)</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="16" t="n">
-        <f aca="false">MIN($K$15*$K$9,G24)</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="16" t="n">
-        <f aca="false">MIN($K$15*$K$9,H24)</f>
+        <v>62</v>
+      </c>
+      <c r="C25" s="17" t="n">
+        <f aca="false">MIN($M$15*$M$9,C24)</f>
+        <v>0</v>
+      </c>
+      <c r="D25" s="17" t="n">
+        <f aca="false">MIN($M$15*$M$9,D24)</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <f aca="false">MIN($M$15*$M$9,E24)</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="17" t="n">
+        <f aca="false">MIN($M$15*$M$9,F24)</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="17" t="n">
+        <f aca="false">MIN($M$15*$M$9,G24)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="17" t="n">
+        <f aca="false">MIN($M$15*$M$9,H24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="16" t="n">
-        <f aca="false">MIN($K$11*C14-C19,C24-C25)</f>
-        <v>0</v>
-      </c>
-      <c r="D26" s="16" t="n">
-        <f aca="false">MIN($K$11*D14-D19,D24-D25)</f>
-        <v>0</v>
-      </c>
-      <c r="E26" s="16" t="n">
-        <f aca="false">MIN($K$11*E14-E19,E24-E25)</f>
-        <v>0</v>
-      </c>
-      <c r="F26" s="16" t="n">
-        <f aca="false">MIN($K$11*F14-F19,F24-F25)</f>
-        <v>0</v>
-      </c>
-      <c r="G26" s="16" t="n">
-        <f aca="false">MIN($K$11*G14-G19,G24-G25)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="16" t="n">
-        <f aca="false">MIN($K$11*H14-H19,H24-H25)</f>
+        <v>69</v>
+      </c>
+      <c r="C26" s="17" t="n">
+        <f aca="false">MIN($M$11*C14-C19,C24-C25)</f>
+        <v>0</v>
+      </c>
+      <c r="D26" s="17" t="n">
+        <f aca="false">MIN($M$11*D14-D19,D24-D25)</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <f aca="false">MIN($M$11*E14-E19,E24-E25)</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="17" t="n">
+        <f aca="false">MIN($M$11*F14-F19,F24-F25)</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="17" t="n">
+        <f aca="false">MIN($M$11*G14-G19,G24-G25)</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="17" t="n">
+        <f aca="false">MIN($M$11*H14-H19,H24-H25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="C27" s="16" t="n">
+        <v>55</v>
+      </c>
+      <c r="C27" s="17" t="n">
         <f aca="false">C24-C25-C26</f>
         <v>0</v>
       </c>
-      <c r="D27" s="16" t="n">
+      <c r="D27" s="17" t="n">
         <f aca="false">D24-D25-D26</f>
         <v>0</v>
       </c>
-      <c r="E27" s="16" t="n">
+      <c r="E27" s="17" t="n">
         <f aca="false">E24-E25-E26</f>
         <v>0</v>
       </c>
-      <c r="F27" s="16" t="n">
+      <c r="F27" s="17" t="n">
         <f aca="false">F24-F25-F26</f>
         <v>0</v>
       </c>
-      <c r="G27" s="16" t="n">
+      <c r="G27" s="17" t="n">
         <f aca="false">G24-G25-G26</f>
         <v>0</v>
       </c>
-      <c r="H27" s="16" t="n">
+      <c r="H27" s="17" t="n">
         <f aca="false">H24-H25-H26</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="C28" s="16" t="n">
-        <f aca="false">C24*$K$10</f>
-        <v>0</v>
-      </c>
-      <c r="D28" s="16" t="n">
-        <f aca="false">D24*$K$10</f>
-        <v>0</v>
-      </c>
-      <c r="E28" s="16" t="n">
-        <f aca="false">E24*$K$10</f>
-        <v>0</v>
-      </c>
-      <c r="F28" s="16" t="n">
-        <f aca="false">F24*$K$10</f>
-        <v>0</v>
-      </c>
-      <c r="G28" s="16" t="n">
-        <f aca="false">G24*$K$10</f>
-        <v>0</v>
-      </c>
-      <c r="H28" s="16" t="n">
-        <f aca="false">H24*$K$10</f>
+        <v>49</v>
+      </c>
+      <c r="C28" s="17" t="n">
+        <f aca="false">C24*$M$10</f>
+        <v>0</v>
+      </c>
+      <c r="D28" s="17" t="n">
+        <f aca="false">D24*$M$10</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <f aca="false">E24*$M$10</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="17" t="n">
+        <f aca="false">F24*$M$10</f>
+        <v>0</v>
+      </c>
+      <c r="G28" s="17" t="n">
+        <f aca="false">G24*$M$10</f>
+        <v>0</v>
+      </c>
+      <c r="H28" s="17" t="n">
+        <f aca="false">H24*$M$10</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C30" s="8" t="n">
         <f aca="false">C13+C20+C27</f>
@@ -1809,7 +1911,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C31" s="8" t="n">
         <f aca="false">C10+C21+C28</f>
@@ -1838,29 +1940,29 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C32" s="20" t="str">
+        <v>72</v>
+      </c>
+      <c r="C32" s="21" t="str">
         <f aca="false">IFERROR(C30/C5,"-")</f>
         <v>-</v>
       </c>
-      <c r="D32" s="20" t="str">
+      <c r="D32" s="21" t="str">
         <f aca="false">IFERROR(D30/D5,"-")</f>
         <v>-</v>
       </c>
-      <c r="E32" s="20" t="str">
+      <c r="E32" s="21" t="str">
         <f aca="false">IFERROR(E30/E5,"-")</f>
         <v>-</v>
       </c>
-      <c r="F32" s="20" t="str">
+      <c r="F32" s="21" t="str">
         <f aca="false">IFERROR(F30/F5,"-")</f>
         <v>-</v>
       </c>
-      <c r="G32" s="20" t="str">
+      <c r="G32" s="21" t="str">
         <f aca="false">IFERROR(G30/G5,"-")</f>
         <v>-</v>
       </c>
-      <c r="H32" s="20" t="str">
+      <c r="H32" s="21" t="str">
         <f aca="false">IFERROR(H30/H5,"-")</f>
         <v>-</v>
       </c>
@@ -1881,7 +1983,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:D33"/>
+  <dimension ref="B2:E33"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -1891,33 +1993,33 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="4" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" s="21" t="n">
+        <v>75</v>
+      </c>
+      <c r="C5" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="22" t="n">
+        <v>76</v>
+      </c>
+      <c r="C6" s="23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C7" s="8" t="n">
         <f aca="false">C5*C6</f>
@@ -1926,38 +2028,51 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" s="23" t="n">
+        <v>78</v>
+      </c>
+      <c r="C8" s="24" t="n">
         <f aca="false">'Sources &amp; Uses'!C9</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="4" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" s="23" t="n">
+        <v>80</v>
+      </c>
+      <c r="C11" s="24" t="n">
         <f aca="false">'Debt Schedule'!H5</f>
         <v>0</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" s="22" t="n">
+        <v>81</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <f aca="false">IFERROR(IF(Cover!$C$11="Downside",E12,D12),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="0" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C13" s="8" t="n">
         <f aca="false">C11*C12</f>
@@ -1966,16 +2081,16 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" s="23" t="n">
+        <v>83</v>
+      </c>
+      <c r="C14" s="24" t="n">
         <f aca="false">'Debt Schedule'!H30</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="0" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C15" s="7" t="n">
         <f aca="false">C13-C14</f>
@@ -1984,142 +2099,142 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" s="24" t="str">
+        <v>86</v>
+      </c>
+      <c r="C18" s="26" t="str">
         <f aca="false">IFERROR(C15/(C8+'Sources &amp; Uses'!C10),"-")</f>
         <v>-</v>
       </c>
-      <c r="D18" s="19" t="s">
-        <v>82</v>
+      <c r="D18" s="20" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="0" t="s">
-        <v>83</v>
-      </c>
-      <c r="C19" s="11" t="n">
+        <v>88</v>
+      </c>
+      <c r="C19" s="10" t="n">
         <f aca="false">Cover!C9</f>
         <v>5</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="0" t="s">
-        <v>84</v>
-      </c>
-      <c r="C20" s="25" t="str">
+        <v>89</v>
+      </c>
+      <c r="C20" s="27" t="str">
         <f aca="false">IFERROR(C18^(1/C19)-1,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="0" t="s">
-        <v>86</v>
-      </c>
-      <c r="C23" s="12" t="n">
+        <v>91</v>
+      </c>
+      <c r="C23" s="11" t="n">
         <f aca="false">'Sources &amp; Uses'!C9+'Sources &amp; Uses'!C10</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="0" t="s">
-        <v>87</v>
-      </c>
-      <c r="C24" s="26" t="str">
+        <v>92</v>
+      </c>
+      <c r="C24" s="14" t="str">
         <f aca="false">IFERROR('Sources &amp; Uses'!C10/C23,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="0" t="s">
-        <v>88</v>
-      </c>
-      <c r="C25" s="14" t="n">
+        <v>93</v>
+      </c>
+      <c r="C25" s="13" t="n">
         <v>0.2</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="0" t="s">
-        <v>89</v>
-      </c>
-      <c r="C26" s="14" t="n">
+        <v>94</v>
+      </c>
+      <c r="C26" s="13" t="n">
         <v>0.2</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="0" t="s">
-        <v>90</v>
-      </c>
-      <c r="C27" s="13" t="n">
+        <v>95</v>
+      </c>
+      <c r="C27" s="12" t="n">
         <f aca="false">IFERROR(C23*(1+C25)^C19,"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="0" t="s">
-        <v>91</v>
-      </c>
-      <c r="C28" s="13" t="n">
+        <v>96</v>
+      </c>
+      <c r="C28" s="12" t="n">
         <f aca="false">MAX(0,C15-C27)</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="0" t="s">
-        <v>92</v>
-      </c>
-      <c r="C29" s="27" t="n">
+        <v>97</v>
+      </c>
+      <c r="C29" s="28" t="n">
         <f aca="false">C28*C26</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="0" t="s">
-        <v>93</v>
-      </c>
-      <c r="C30" s="27" t="str">
+        <v>98</v>
+      </c>
+      <c r="C30" s="28" t="str">
         <f aca="false">IFERROR(C24*C15+C29,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="0" t="s">
-        <v>94</v>
-      </c>
-      <c r="C31" s="27" t="str">
+        <v>99</v>
+      </c>
+      <c r="C31" s="28" t="str">
         <f aca="false">IFERROR(C15-C30,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="0" t="s">
-        <v>95</v>
-      </c>
-      <c r="C32" s="28" t="str">
+        <v>100</v>
+      </c>
+      <c r="C32" s="29" t="str">
         <f aca="false">IFERROR(C31/'Sources &amp; Uses'!C9,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="C33" s="29" t="str">
+        <v>101</v>
+      </c>
+      <c r="C33" s="30" t="str">
         <f aca="false">IFERROR(C32^(1/C19)-1,"-")</f>
         <v>-</v>
       </c>
-      <c r="D33" s="19" t="s">
-        <v>97</v>
+      <c r="D33" s="20" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -2148,127 +2263,127 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C4" s="30" t="n">
+        <v>104</v>
+      </c>
+      <c r="C4" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="D4" s="30" t="n">
+      <c r="D4" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="30" t="n">
+      <c r="E4" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="F4" s="30" t="n">
+      <c r="F4" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="G4" s="30" t="n">
+      <c r="G4" s="31" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="30" t="n">
+      <c r="B5" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="C5" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="G5" s="19" t="s">
-        <v>100</v>
+      <c r="C5" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="30" t="n">
+      <c r="B6" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="C6" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="G6" s="19" t="s">
-        <v>100</v>
+      <c r="C6" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="30" t="n">
+      <c r="B7" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="C7" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="G7" s="19" t="s">
-        <v>100</v>
+      <c r="C7" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="30" t="n">
+      <c r="B8" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="C8" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="F8" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="G8" s="19" t="s">
-        <v>100</v>
+      <c r="C8" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="30" t="n">
+      <c r="B9" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="C9" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="G9" s="19" t="s">
-        <v>100</v>
+      <c r="C9" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -2299,24 +2414,24 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="9" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/03_Private_Equity/_template_LBO.xlsx
+++ b/03_Private_Equity/_template_LBO.xlsx
@@ -524,132 +524,136 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -908,76 +912,76 @@
   <dimension ref="B2:C11"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="4"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="3"/>
+      <c r="C4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" s="4" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1000,126 +1004,126 @@
   <dimension ref="B2:F13"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="5" t="s">
+      <c r="C5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="C6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="5" t="s">
+      <c r="C7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="5" t="s">
+      <c r="C8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="5" t="s">
+      <c r="C9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="C10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="F10" s="8" t="n">
         <f aca="false">SUM(F5:F9)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="8" t="n">
         <f aca="false">SUM(C5:C10)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="8" t="n">
+      <c r="C13" s="9" t="n">
         <f aca="false">C11-F10</f>
         <v>0</v>
       </c>
@@ -1143,826 +1147,826 @@
   <dimension ref="B2:M32"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="14"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="L4" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="M4" s="9" t="s">
+      <c r="M4" s="10" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C5" s="12" t="n">
         <f aca="false">Returns!C5</f>
         <v>0</v>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="13" t="n">
         <f aca="false">C5*(1+$M$5)</f>
         <v>0</v>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="13" t="n">
         <f aca="false">D5*(1+$M$5)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="12" t="n">
+      <c r="F5" s="13" t="n">
         <f aca="false">E5*(1+$M$5)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="12" t="n">
+      <c r="G5" s="13" t="n">
         <f aca="false">F5*(1+$M$5)</f>
         <v>0</v>
       </c>
-      <c r="H5" s="12" t="n">
+      <c r="H5" s="13" t="n">
         <f aca="false">G5*(1+$M$5)</f>
         <v>0</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="K5" s="13" t="n">
+      <c r="K5" s="14" t="n">
         <v>0.05</v>
       </c>
-      <c r="L5" s="13" t="n">
+      <c r="L5" s="14" t="n">
         <v>-0.03</v>
       </c>
-      <c r="M5" s="14" t="n">
+      <c r="M5" s="15" t="n">
         <f aca="false">IF(Cover!$C$11="Downside",L5,K5)</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="13" t="n">
         <f aca="false">C5*$M$6</f>
         <v>0</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="13" t="n">
         <f aca="false">D5*$M$6</f>
         <v>0</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="13" t="n">
         <f aca="false">E5*$M$6</f>
         <v>0</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="13" t="n">
         <f aca="false">F5*$M$6</f>
         <v>0</v>
       </c>
-      <c r="G6" s="12" t="n">
+      <c r="G6" s="13" t="n">
         <f aca="false">G5*$M$6</f>
         <v>0</v>
       </c>
-      <c r="H6" s="12" t="n">
+      <c r="H6" s="13" t="n">
         <f aca="false">H5*$M$6</f>
         <v>0</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="K6" s="13" t="n">
+      <c r="K6" s="14" t="n">
         <v>0.5</v>
       </c>
-      <c r="L6" s="13" t="n">
+      <c r="L6" s="14" t="n">
         <v>0.35</v>
       </c>
-      <c r="M6" s="14" t="n">
+      <c r="M6" s="15" t="n">
         <f aca="false">IF(Cover!$C$11="Downside",L6,K6)</f>
         <v>0.5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="K7" s="13" t="n">
+      <c r="K7" s="14" t="n">
         <v>0.05</v>
       </c>
-      <c r="L7" s="13" t="n">
+      <c r="L7" s="14" t="n">
         <v>0.05</v>
       </c>
-      <c r="M7" s="14" t="n">
+      <c r="M7" s="15" t="n">
         <f aca="false">IF(Cover!$C$11="Downside",L7,K7)</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="J8" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="K8" s="15" t="n">
+      <c r="K8" s="16" t="n">
         <v>0.07</v>
       </c>
-      <c r="L8" s="15" t="n">
+      <c r="L8" s="16" t="n">
         <v>0.085</v>
       </c>
-      <c r="M8" s="16" t="n">
+      <c r="M8" s="17" t="n">
         <f aca="false">IF(Cover!$C$11="Downside",L8,K8)</f>
         <v>0.07</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="17" t="n">
+      <c r="C9" s="18" t="n">
         <f aca="false">$M$16</f>
         <v>0</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="18" t="n">
         <f aca="false">C13</f>
         <v>0</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="18" t="n">
         <f aca="false">D13</f>
         <v>0</v>
       </c>
-      <c r="F9" s="17" t="n">
+      <c r="F9" s="18" t="n">
         <f aca="false">E13</f>
         <v>0</v>
       </c>
-      <c r="G9" s="17" t="n">
+      <c r="G9" s="18" t="n">
         <f aca="false">F13</f>
         <v>0</v>
       </c>
-      <c r="H9" s="17" t="n">
+      <c r="H9" s="18" t="n">
         <f aca="false">G13</f>
         <v>0</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="J9" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="K9" s="13" t="n">
+      <c r="K9" s="14" t="n">
         <v>0.01</v>
       </c>
-      <c r="L9" s="13" t="n">
+      <c r="L9" s="14" t="n">
         <v>0.01</v>
       </c>
-      <c r="M9" s="14" t="n">
+      <c r="M9" s="15" t="n">
         <f aca="false">IF(Cover!$C$11="Downside",L9,K9)</f>
         <v>0.01</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="18" t="n">
         <f aca="false">C9*$M$13</f>
         <v>0</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="18" t="n">
         <f aca="false">D9*$M$13</f>
         <v>0</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="18" t="n">
         <f aca="false">E9*$M$13</f>
         <v>0</v>
       </c>
-      <c r="F10" s="17" t="n">
+      <c r="F10" s="18" t="n">
         <f aca="false">F9*$M$13</f>
         <v>0</v>
       </c>
-      <c r="G10" s="17" t="n">
+      <c r="G10" s="18" t="n">
         <f aca="false">G9*$M$13</f>
         <v>0</v>
       </c>
-      <c r="H10" s="17" t="n">
+      <c r="H10" s="18" t="n">
         <f aca="false">H9*$M$13</f>
         <v>0</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="J10" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="K10" s="15" t="n">
+      <c r="K10" s="16" t="n">
         <v>0.095</v>
       </c>
-      <c r="L10" s="15" t="n">
+      <c r="L10" s="16" t="n">
         <v>0.115</v>
       </c>
-      <c r="M10" s="16" t="n">
+      <c r="M10" s="17" t="n">
         <f aca="false">IF(Cover!$C$11="Downside",L10,K10)</f>
         <v>0.095</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="17" t="n">
+      <c r="C11" s="18" t="n">
         <f aca="false">C6-C18-C25-C10-C21-C28</f>
         <v>0</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="18" t="n">
         <f aca="false">D6-D18-D25-D10-D21-D28</f>
         <v>0</v>
       </c>
-      <c r="E11" s="17" t="n">
+      <c r="E11" s="18" t="n">
         <f aca="false">E6-E18-E25-E10-E21-E28</f>
         <v>0</v>
       </c>
-      <c r="F11" s="17" t="n">
+      <c r="F11" s="18" t="n">
         <f aca="false">F6-F18-F25-F10-F21-F28</f>
         <v>0</v>
       </c>
-      <c r="G11" s="17" t="n">
+      <c r="G11" s="18" t="n">
         <f aca="false">G6-G18-G25-G10-G21-G28</f>
         <v>0</v>
       </c>
-      <c r="H11" s="17" t="n">
+      <c r="H11" s="18" t="n">
         <f aca="false">H6-H18-H25-H10-H21-H28</f>
         <v>0</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="J11" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="K11" s="13" t="n">
+      <c r="K11" s="14" t="n">
         <v>0.75</v>
       </c>
-      <c r="L11" s="13" t="n">
+      <c r="L11" s="14" t="n">
         <v>0.75</v>
       </c>
-      <c r="M11" s="14" t="n">
+      <c r="M11" s="15" t="n">
         <f aca="false">IF(Cover!$C$11="Downside",L11,K11)</f>
         <v>0.75</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="17" t="n">
+      <c r="C12" s="18" t="n">
         <f aca="false">IF(C11&lt;0,MIN(-C11,$M$12-C9),-MIN(C9,MAX(0,C11)))</f>
         <v>-0</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="18" t="n">
         <f aca="false">IF(D11&lt;0,MIN(-D11,$M$12-D9),-MIN(D9,MAX(0,D11)))</f>
         <v>-0</v>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="18" t="n">
         <f aca="false">IF(E11&lt;0,MIN(-E11,$M$12-E9),-MIN(E9,MAX(0,E11)))</f>
         <v>-0</v>
       </c>
-      <c r="F12" s="17" t="n">
+      <c r="F12" s="18" t="n">
         <f aca="false">IF(F11&lt;0,MIN(-F11,$M$12-F9),-MIN(F9,MAX(0,F11)))</f>
         <v>-0</v>
       </c>
-      <c r="G12" s="17" t="n">
+      <c r="G12" s="18" t="n">
         <f aca="false">IF(G11&lt;0,MIN(-G11,$M$12-G9),-MIN(G9,MAX(0,G11)))</f>
         <v>-0</v>
       </c>
-      <c r="H12" s="17" t="n">
+      <c r="H12" s="18" t="n">
         <f aca="false">IF(H11&lt;0,MIN(-H11,$M$12-H9),-MIN(H9,MAX(0,H11)))</f>
         <v>-0</v>
       </c>
-      <c r="J12" s="5" t="s">
+      <c r="J12" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="K12" s="18" t="n">
+      <c r="K12" s="19" t="n">
         <v>50</v>
       </c>
-      <c r="L12" s="18" t="n">
+      <c r="L12" s="19" t="n">
         <v>50</v>
       </c>
-      <c r="M12" s="11" t="n">
+      <c r="M12" s="12" t="n">
         <f aca="false">IF(Cover!$C$11="Downside",L12,K12)</f>
         <v>50</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C13" s="17" t="n">
+      <c r="C13" s="18" t="n">
         <f aca="false">C9+C12</f>
         <v>0</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="18" t="n">
         <f aca="false">D9+D12</f>
         <v>0</v>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="18" t="n">
         <f aca="false">E9+E12</f>
         <v>0</v>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F13" s="18" t="n">
         <f aca="false">F9+F12</f>
         <v>0</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G13" s="18" t="n">
         <f aca="false">G9+G12</f>
         <v>0</v>
       </c>
-      <c r="H13" s="17" t="n">
+      <c r="H13" s="18" t="n">
         <f aca="false">H9+H12</f>
         <v>0</v>
       </c>
-      <c r="J13" s="5" t="s">
+      <c r="J13" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="K13" s="15" t="n">
+      <c r="K13" s="16" t="n">
         <v>0.08</v>
       </c>
-      <c r="L13" s="15" t="n">
+      <c r="L13" s="16" t="n">
         <v>0.095</v>
       </c>
-      <c r="M13" s="16" t="n">
+      <c r="M13" s="17" t="n">
         <f aca="false">IF(Cover!$C$11="Downside",L13,K13)</f>
         <v>0.08</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="18" t="n">
         <f aca="false">MAX(0,MAX(0,C11)-C9)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="18" t="n">
         <f aca="false">MAX(0,MAX(0,D11)-D9)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="17" t="n">
+      <c r="E14" s="18" t="n">
         <f aca="false">MAX(0,MAX(0,E11)-E9)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="17" t="n">
+      <c r="F14" s="18" t="n">
         <f aca="false">MAX(0,MAX(0,F11)-F9)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="17" t="n">
+      <c r="G14" s="18" t="n">
         <f aca="false">MAX(0,MAX(0,G11)-G9)</f>
         <v>0</v>
       </c>
-      <c r="H14" s="17" t="n">
+      <c r="H14" s="18" t="n">
         <f aca="false">MAX(0,MAX(0,H11)-H9)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="19" t="s">
+      <c r="J14" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="M14" s="11" t="n">
+      <c r="M14" s="12" t="n">
         <f aca="false">'Sources &amp; Uses'!C6</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J15" s="0" t="s">
+      <c r="J15" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="M15" s="11" t="n">
+      <c r="M15" s="12" t="n">
         <f aca="false">'Sources &amp; Uses'!C7</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="J16" s="19" t="s">
+      <c r="J16" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="M16" s="11" t="n">
+      <c r="M16" s="12" t="n">
         <f aca="false">'Sources &amp; Uses'!C5</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="17" t="n">
+      <c r="C17" s="18" t="n">
         <f aca="false">$M$14</f>
         <v>0</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="18" t="n">
         <f aca="false">C20</f>
         <v>0</v>
       </c>
-      <c r="E17" s="17" t="n">
+      <c r="E17" s="18" t="n">
         <f aca="false">D20</f>
         <v>0</v>
       </c>
-      <c r="F17" s="17" t="n">
+      <c r="F17" s="18" t="n">
         <f aca="false">E20</f>
         <v>0</v>
       </c>
-      <c r="G17" s="17" t="n">
+      <c r="G17" s="18" t="n">
         <f aca="false">F20</f>
         <v>0</v>
       </c>
-      <c r="H17" s="17" t="n">
+      <c r="H17" s="18" t="n">
         <f aca="false">G20</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C18" s="17" t="n">
+      <c r="C18" s="18" t="n">
         <f aca="false">MIN($M$14*$M$7,C17)</f>
         <v>0</v>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="18" t="n">
         <f aca="false">MIN($M$14*$M$7,D17)</f>
         <v>0</v>
       </c>
-      <c r="E18" s="17" t="n">
+      <c r="E18" s="18" t="n">
         <f aca="false">MIN($M$14*$M$7,E17)</f>
         <v>0</v>
       </c>
-      <c r="F18" s="17" t="n">
+      <c r="F18" s="18" t="n">
         <f aca="false">MIN($M$14*$M$7,F17)</f>
         <v>0</v>
       </c>
-      <c r="G18" s="17" t="n">
+      <c r="G18" s="18" t="n">
         <f aca="false">MIN($M$14*$M$7,G17)</f>
         <v>0</v>
       </c>
-      <c r="H18" s="17" t="n">
+      <c r="H18" s="18" t="n">
         <f aca="false">MIN($M$14*$M$7,H17)</f>
         <v>0</v>
       </c>
-      <c r="J18" s="20" t="s">
+      <c r="J18" s="21" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="17" t="n">
+      <c r="C19" s="18" t="n">
         <f aca="false">MIN($M$11*C14,C17-C18)</f>
         <v>0</v>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D19" s="18" t="n">
         <f aca="false">MIN($M$11*D14,D17-D18)</f>
         <v>0</v>
       </c>
-      <c r="E19" s="17" t="n">
+      <c r="E19" s="18" t="n">
         <f aca="false">MIN($M$11*E14,E17-E18)</f>
         <v>0</v>
       </c>
-      <c r="F19" s="17" t="n">
+      <c r="F19" s="18" t="n">
         <f aca="false">MIN($M$11*F14,F17-F18)</f>
         <v>0</v>
       </c>
-      <c r="G19" s="17" t="n">
+      <c r="G19" s="18" t="n">
         <f aca="false">MIN($M$11*G14,G17-G18)</f>
         <v>0</v>
       </c>
-      <c r="H19" s="17" t="n">
+      <c r="H19" s="18" t="n">
         <f aca="false">MIN($M$11*H14,H17-H18)</f>
         <v>0</v>
       </c>
-      <c r="J19" s="20" t="s">
+      <c r="J19" s="21" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="17" t="n">
+      <c r="C20" s="18" t="n">
         <f aca="false">C17-C18-C19</f>
         <v>0</v>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="D20" s="18" t="n">
         <f aca="false">D17-D18-D19</f>
         <v>0</v>
       </c>
-      <c r="E20" s="17" t="n">
+      <c r="E20" s="18" t="n">
         <f aca="false">E17-E18-E19</f>
         <v>0</v>
       </c>
-      <c r="F20" s="17" t="n">
+      <c r="F20" s="18" t="n">
         <f aca="false">F17-F18-F19</f>
         <v>0</v>
       </c>
-      <c r="G20" s="17" t="n">
+      <c r="G20" s="18" t="n">
         <f aca="false">G17-G18-G19</f>
         <v>0</v>
       </c>
-      <c r="H20" s="17" t="n">
+      <c r="H20" s="18" t="n">
         <f aca="false">H17-H18-H19</f>
         <v>0</v>
       </c>
-      <c r="J20" s="20" t="s">
+      <c r="J20" s="21" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="17" t="n">
+      <c r="C21" s="18" t="n">
         <f aca="false">C17*$M$8</f>
         <v>0</v>
       </c>
-      <c r="D21" s="17" t="n">
+      <c r="D21" s="18" t="n">
         <f aca="false">D17*$M$8</f>
         <v>0</v>
       </c>
-      <c r="E21" s="17" t="n">
+      <c r="E21" s="18" t="n">
         <f aca="false">E17*$M$8</f>
         <v>0</v>
       </c>
-      <c r="F21" s="17" t="n">
+      <c r="F21" s="18" t="n">
         <f aca="false">F17*$M$8</f>
         <v>0</v>
       </c>
-      <c r="G21" s="17" t="n">
+      <c r="G21" s="18" t="n">
         <f aca="false">G17*$M$8</f>
         <v>0</v>
       </c>
-      <c r="H21" s="17" t="n">
+      <c r="H21" s="18" t="n">
         <f aca="false">H17*$M$8</f>
         <v>0</v>
       </c>
-      <c r="J21" s="20" t="s">
+      <c r="J21" s="21" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="3" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="17" t="n">
+      <c r="C24" s="18" t="n">
         <f aca="false">$M$15</f>
         <v>0</v>
       </c>
-      <c r="D24" s="17" t="n">
+      <c r="D24" s="18" t="n">
         <f aca="false">C27</f>
         <v>0</v>
       </c>
-      <c r="E24" s="17" t="n">
+      <c r="E24" s="18" t="n">
         <f aca="false">D27</f>
         <v>0</v>
       </c>
-      <c r="F24" s="17" t="n">
+      <c r="F24" s="18" t="n">
         <f aca="false">E27</f>
         <v>0</v>
       </c>
-      <c r="G24" s="17" t="n">
+      <c r="G24" s="18" t="n">
         <f aca="false">F27</f>
         <v>0</v>
       </c>
-      <c r="H24" s="17" t="n">
+      <c r="H24" s="18" t="n">
         <f aca="false">G27</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="17" t="n">
+      <c r="C25" s="18" t="n">
         <f aca="false">MIN($M$15*$M$9,C24)</f>
         <v>0</v>
       </c>
-      <c r="D25" s="17" t="n">
+      <c r="D25" s="18" t="n">
         <f aca="false">MIN($M$15*$M$9,D24)</f>
         <v>0</v>
       </c>
-      <c r="E25" s="17" t="n">
+      <c r="E25" s="18" t="n">
         <f aca="false">MIN($M$15*$M$9,E24)</f>
         <v>0</v>
       </c>
-      <c r="F25" s="17" t="n">
+      <c r="F25" s="18" t="n">
         <f aca="false">MIN($M$15*$M$9,F24)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="17" t="n">
+      <c r="G25" s="18" t="n">
         <f aca="false">MIN($M$15*$M$9,G24)</f>
         <v>0</v>
       </c>
-      <c r="H25" s="17" t="n">
+      <c r="H25" s="18" t="n">
         <f aca="false">MIN($M$15*$M$9,H24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C26" s="17" t="n">
+      <c r="C26" s="18" t="n">
         <f aca="false">MIN($M$11*C14-C19,C24-C25)</f>
         <v>0</v>
       </c>
-      <c r="D26" s="17" t="n">
+      <c r="D26" s="18" t="n">
         <f aca="false">MIN($M$11*D14-D19,D24-D25)</f>
         <v>0</v>
       </c>
-      <c r="E26" s="17" t="n">
+      <c r="E26" s="18" t="n">
         <f aca="false">MIN($M$11*E14-E19,E24-E25)</f>
         <v>0</v>
       </c>
-      <c r="F26" s="17" t="n">
+      <c r="F26" s="18" t="n">
         <f aca="false">MIN($M$11*F14-F19,F24-F25)</f>
         <v>0</v>
       </c>
-      <c r="G26" s="17" t="n">
+      <c r="G26" s="18" t="n">
         <f aca="false">MIN($M$11*G14-G19,G24-G25)</f>
         <v>0</v>
       </c>
-      <c r="H26" s="17" t="n">
+      <c r="H26" s="18" t="n">
         <f aca="false">MIN($M$11*H14-H19,H24-H25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="17" t="n">
+      <c r="C27" s="18" t="n">
         <f aca="false">C24-C25-C26</f>
         <v>0</v>
       </c>
-      <c r="D27" s="17" t="n">
+      <c r="D27" s="18" t="n">
         <f aca="false">D24-D25-D26</f>
         <v>0</v>
       </c>
-      <c r="E27" s="17" t="n">
+      <c r="E27" s="18" t="n">
         <f aca="false">E24-E25-E26</f>
         <v>0</v>
       </c>
-      <c r="F27" s="17" t="n">
+      <c r="F27" s="18" t="n">
         <f aca="false">F24-F25-F26</f>
         <v>0</v>
       </c>
-      <c r="G27" s="17" t="n">
+      <c r="G27" s="18" t="n">
         <f aca="false">G24-G25-G26</f>
         <v>0</v>
       </c>
-      <c r="H27" s="17" t="n">
+      <c r="H27" s="18" t="n">
         <f aca="false">H24-H25-H26</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="17" t="n">
+      <c r="C28" s="18" t="n">
         <f aca="false">C24*$M$10</f>
         <v>0</v>
       </c>
-      <c r="D28" s="17" t="n">
+      <c r="D28" s="18" t="n">
         <f aca="false">D24*$M$10</f>
         <v>0</v>
       </c>
-      <c r="E28" s="17" t="n">
+      <c r="E28" s="18" t="n">
         <f aca="false">E24*$M$10</f>
         <v>0</v>
       </c>
-      <c r="F28" s="17" t="n">
+      <c r="F28" s="18" t="n">
         <f aca="false">F24*$M$10</f>
         <v>0</v>
       </c>
-      <c r="G28" s="17" t="n">
+      <c r="G28" s="18" t="n">
         <f aca="false">G24*$M$10</f>
         <v>0</v>
       </c>
-      <c r="H28" s="17" t="n">
+      <c r="H28" s="18" t="n">
         <f aca="false">H24*$M$10</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C30" s="8" t="n">
+      <c r="C30" s="9" t="n">
         <f aca="false">C13+C20+C27</f>
         <v>0</v>
       </c>
-      <c r="D30" s="8" t="n">
+      <c r="D30" s="9" t="n">
         <f aca="false">D13+D20+D27</f>
         <v>0</v>
       </c>
-      <c r="E30" s="8" t="n">
+      <c r="E30" s="9" t="n">
         <f aca="false">E13+E20+E27</f>
         <v>0</v>
       </c>
-      <c r="F30" s="8" t="n">
+      <c r="F30" s="9" t="n">
         <f aca="false">F13+F20+F27</f>
         <v>0</v>
       </c>
-      <c r="G30" s="8" t="n">
+      <c r="G30" s="9" t="n">
         <f aca="false">G13+G20+G27</f>
         <v>0</v>
       </c>
-      <c r="H30" s="8" t="n">
+      <c r="H30" s="9" t="n">
         <f aca="false">H13+H20+H27</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C31" s="8" t="n">
+      <c r="C31" s="9" t="n">
         <f aca="false">C10+C21+C28</f>
         <v>0</v>
       </c>
-      <c r="D31" s="8" t="n">
+      <c r="D31" s="9" t="n">
         <f aca="false">D10+D21+D28</f>
         <v>0</v>
       </c>
-      <c r="E31" s="8" t="n">
+      <c r="E31" s="9" t="n">
         <f aca="false">E10+E21+E28</f>
         <v>0</v>
       </c>
-      <c r="F31" s="8" t="n">
+      <c r="F31" s="9" t="n">
         <f aca="false">F10+F21+F28</f>
         <v>0</v>
       </c>
-      <c r="G31" s="8" t="n">
+      <c r="G31" s="9" t="n">
         <f aca="false">G10+G21+G28</f>
         <v>0</v>
       </c>
-      <c r="H31" s="8" t="n">
+      <c r="H31" s="9" t="n">
         <f aca="false">H10+H21+H28</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C32" s="21" t="str">
+      <c r="C32" s="22" t="str">
         <f aca="false">IFERROR(C30/C5,"-")</f>
         <v>-</v>
       </c>
-      <c r="D32" s="21" t="str">
+      <c r="D32" s="22" t="str">
         <f aca="false">IFERROR(D30/D5,"-")</f>
         <v>-</v>
       </c>
-      <c r="E32" s="21" t="str">
+      <c r="E32" s="22" t="str">
         <f aca="false">IFERROR(E30/E5,"-")</f>
         <v>-</v>
       </c>
-      <c r="F32" s="21" t="str">
+      <c r="F32" s="22" t="str">
         <f aca="false">IFERROR(F30/F5,"-")</f>
         <v>-</v>
       </c>
-      <c r="G32" s="21" t="str">
+      <c r="G32" s="22" t="str">
         <f aca="false">IFERROR(G30/G5,"-")</f>
         <v>-</v>
       </c>
-      <c r="H32" s="21" t="str">
+      <c r="H32" s="22" t="str">
         <f aca="false">IFERROR(H30/H5,"-")</f>
         <v>-</v>
       </c>
@@ -1986,254 +1990,254 @@
   <dimension ref="B2:E33"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="1" width="14"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C5" s="22" t="n">
+      <c r="C5" s="23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C6" s="23" t="n">
+      <c r="C6" s="24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="9" t="n">
         <f aca="false">C5*C6</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C8" s="24" t="n">
+      <c r="C8" s="25" t="n">
         <f aca="false">'Sources &amp; Uses'!C9</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C11" s="24" t="n">
+      <c r="C11" s="25" t="n">
         <f aca="false">'Debt Schedule'!H5</f>
         <v>0</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="3" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="25" t="n">
+      <c r="C12" s="26" t="n">
         <f aca="false">IFERROR(IF(Cover!$C$11="Downside",E12,D12),"-")</f>
         <v>0</v>
       </c>
-      <c r="D12" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="23" t="n">
+      <c r="D12" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C13" s="8" t="n">
+      <c r="C13" s="9" t="n">
         <f aca="false">C11*C12</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C14" s="24" t="n">
+      <c r="C14" s="25" t="n">
         <f aca="false">'Debt Schedule'!H30</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="8" t="n">
         <f aca="false">C13-C14</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C18" s="26" t="str">
+      <c r="C18" s="27" t="str">
         <f aca="false">IFERROR(C15/(C8+'Sources &amp; Uses'!C10),"-")</f>
         <v>-</v>
       </c>
-      <c r="D18" s="20" t="s">
+      <c r="D18" s="21" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C19" s="10" t="n">
+      <c r="C19" s="11" t="n">
         <f aca="false">Cover!C9</f>
         <v>5</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C20" s="27" t="str">
+      <c r="C20" s="28" t="str">
         <f aca="false">IFERROR(C18^(1/C19)-1,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C23" s="11" t="n">
+      <c r="C23" s="12" t="n">
         <f aca="false">'Sources &amp; Uses'!C9+'Sources &amp; Uses'!C10</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C24" s="14" t="str">
+      <c r="C24" s="15" t="str">
         <f aca="false">IFERROR('Sources &amp; Uses'!C10/C23,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C25" s="13" t="n">
+      <c r="C25" s="14" t="n">
         <v>0.2</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C26" s="13" t="n">
+      <c r="C26" s="14" t="n">
         <v>0.2</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C27" s="12" t="n">
+      <c r="C27" s="13" t="n">
         <f aca="false">IFERROR(C23*(1+C25)^C19,"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C28" s="12" t="n">
+      <c r="C28" s="13" t="n">
         <f aca="false">MAX(0,C15-C27)</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="0" t="s">
+      <c r="B29" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C29" s="28" t="n">
+      <c r="C29" s="29" t="n">
         <f aca="false">C28*C26</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="0" t="s">
+      <c r="B30" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C30" s="28" t="str">
+      <c r="C30" s="29" t="str">
         <f aca="false">IFERROR(C24*C15+C29,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C31" s="28" t="str">
+      <c r="C31" s="29" t="str">
         <f aca="false">IFERROR(C15-C30,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="0" t="s">
+      <c r="B32" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C32" s="29" t="str">
+      <c r="C32" s="30" t="str">
         <f aca="false">IFERROR(C31/'Sources &amp; Uses'!C9,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="0" t="s">
+      <c r="B33" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C33" s="30" t="str">
+      <c r="C33" s="31" t="str">
         <f aca="false">IFERROR(C32^(1/C19)-1,"-")</f>
         <v>-</v>
       </c>
-      <c r="D33" s="20" t="s">
+      <c r="D33" s="21" t="s">
         <v>102</v>
       </c>
     </row>
@@ -2256,133 +2260,133 @@
   <dimension ref="B2:G9"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="12"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C4" s="31" t="n">
+      <c r="C4" s="32" t="n">
         <v>7</v>
       </c>
-      <c r="D4" s="31" t="n">
+      <c r="D4" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="31" t="n">
+      <c r="E4" s="32" t="n">
         <v>9</v>
       </c>
-      <c r="F4" s="31" t="n">
+      <c r="F4" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="G4" s="31" t="n">
+      <c r="G4" s="32" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="31" t="n">
+      <c r="B5" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="F5" s="20" t="s">
+      <c r="F5" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="G5" s="21" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="31" t="n">
+      <c r="B6" s="32" t="n">
         <v>7</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="G6" s="20" t="s">
+      <c r="G6" s="21" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="31" t="n">
+      <c r="B7" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="G7" s="21" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="31" t="n">
+      <c r="B8" s="32" t="n">
         <v>9</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="F8" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="G8" s="20" t="s">
+      <c r="G8" s="21" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="31" t="n">
+      <c r="B9" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="E9" s="20" t="s">
+      <c r="E9" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="F9" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="G9" s="20" t="s">
+      <c r="G9" s="21" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2405,32 +2409,32 @@
   <dimension ref="B2:F4"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="10" t="s">
         <v>111</v>
       </c>
     </row>

--- a/03_Private_Equity/_template_LBO.xlsx
+++ b/03_Private_Equity/_template_LBO.xlsx
@@ -13,7 +13,9 @@
     <sheet name="Debt Schedule" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Returns" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Sensitivity" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="RefreshLog" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Sources" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Checks" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="RefreshLog" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="142">
   <si>
     <t xml:space="preserve">[TARGET] — LBO Model</t>
   </si>
@@ -343,6 +345,96 @@
   </si>
   <si>
     <t xml:space="preserve">[data table — Excel What-If Analysis]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What each material assumption or convention in this model comes from.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption / convention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-tranche cash sweep priority (revolver, then TLA, then TLB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard leveraged-loan credit-agreement absolute-priority cash sweep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard practice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real credit agreements can have more nuanced sweep mechanics (e.g. leverage-based step-downs, as modeled in the Private Credit archetype) -- this uses strict seniority order only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interest computed off beginning-of-period balances only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modeling convention used throughout this repository to avoid circular references</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matches the Private Credit and Project Finance debt schedules' convention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Management promote / ratchet above an IRR hurdle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard PE deal-level management incentive structure, mechanically identical to a GP catch-up (see the Asset Management archetype's fee waterfall for the fund-side analogue)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single hurdle/promote tier -- no multi-tier ratchet (increasing promote % at higher IRR bands), which some deals use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exit multiple is scenario-aware (Base/Downside); entry multiple is not</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modeling choice: entry multiple is a contractual fact of the deal that already happened, exit multiple is the genuine forward uncertainty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modeling choice, documented on the Returns tab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A downside case pairs worse operating performance with multiple compression -- a distressed exit is punished twice, not once on EBITDA alone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live reconciliation identities -- independent of the model's own formulas, must tie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Result</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passes when</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sources = Uses at close</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 (exact)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total debt ties: revolver+TLA+TLB ending balances = Total debt row (Yr5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sponsor-only IRR never exceeds blended IRR (promote only transfers value away from the sponsor, never adds to it)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active debt-schedule assumptions match the Cover scenario selector</t>
   </si>
   <si>
     <t xml:space="preserve">Refresh Log</t>
@@ -367,12 +459,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%;\(0.0%\);\-"/>
     <numFmt numFmtId="167" formatCode="0.00%;\(0.00%\);\-"/>
     <numFmt numFmtId="168" formatCode="0.0\x"/>
+    <numFmt numFmtId="169" formatCode="General"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -524,7 +617,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -654,6 +747,18 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2406,6 +2511,206 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="B2:E9"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="46"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="21" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="D6" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="E6" s="34" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="33" t="s">
+        <v>115</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>116</v>
+      </c>
+      <c r="D7" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="E7" s="34" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="D8" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="33" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="D9" s="33" t="s">
+        <v>123</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>124</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:D9"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="46"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="21" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="C6" s="29" t="n">
+        <f aca="false">'Sources &amp; Uses'!C13</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="33" t="s">
+        <v>132</v>
+      </c>
+      <c r="C7" s="35" t="n">
+        <f aca="false">'Debt Schedule'!H30-('Debt Schedule'!H13+'Debt Schedule'!H20+'Debt Schedule'!H27)</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="C8" s="35" t="b">
+        <f aca="false">IF(OR(NOT(ISNUMBER(Returns!C33)),NOT(ISNUMBER(Returns!C20))),TRUE(),Returns!C33&lt;=Returns!C20+0.0000001)</f>
+        <v>1</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="C9" s="35" t="b">
+        <f aca="false">IF(Cover!$C$11="Downside",'Debt Schedule'!M5='Debt Schedule'!L5,'Debt Schedule'!M5='Debt Schedule'!K5)</f>
+        <v>1</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>134</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="B2:F4"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -2418,24 +2723,24 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="10" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
